--- a/downloads/exportExelCustomerFilter3.xlsx
+++ b/downloads/exportExelCustomerFilter3.xlsx
@@ -46,7 +46,7 @@
     <t>commercial</t>
   </si>
   <si>
-    <t>8000000005</t>
+    <t>9863576112</t>
   </si>
   <si>
     <t>Sushil Kumar</t>
@@ -61,7 +61,7 @@
     <t>1345836</t>
   </si>
   <si>
-    <t>8000000003</t>
+    <t>9863574192</t>
   </si>
   <si>
     <t>Sushil Singh</t>
@@ -76,7 +76,7 @@
     <t>1245836</t>
   </si>
   <si>
-    <t>8000000001</t>
+    <t>9863574112</t>
   </si>
 </sst>
 </file>
